--- a/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR MURGO LORENZO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR MURGO LORENZO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>

--- a/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR MURGO LORENZO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR MURGO LORENZO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>

--- a/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR MURGO LORENZO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR MURGO LORENZO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
